--- a/reports/relatorio_sim.xlsx
+++ b/reports/relatorio_sim.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="60">
   <si>
     <t>CID</t>
   </si>
@@ -61,25 +61,139 @@
     <t>B572</t>
   </si>
   <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Sucupira Do Norte</t>
+  </si>
+  <si>
+    <t>B570</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Pinheiro</t>
+  </si>
+  <si>
+    <t>Codó</t>
+  </si>
+  <si>
+    <t>São Raimundo das Mangabeiras</t>
+  </si>
+  <si>
+    <t>B573</t>
+  </si>
+  <si>
+    <t>Turilândia</t>
+  </si>
+  <si>
+    <t>Estreito</t>
+  </si>
+  <si>
+    <t>Presidente Juscelino</t>
+  </si>
+  <si>
+    <t>Itaipava do Grajaú</t>
+  </si>
+  <si>
+    <t>Mirador</t>
+  </si>
+  <si>
+    <t>B571</t>
+  </si>
+  <si>
+    <t>Grajaú</t>
+  </si>
+  <si>
+    <t>Arame</t>
+  </si>
+  <si>
+    <t>Cajapió</t>
+  </si>
+  <si>
+    <t>São Francisco Do Brejão</t>
+  </si>
+  <si>
+    <t>B575</t>
+  </si>
+  <si>
+    <t>Pio Xii</t>
+  </si>
+  <si>
+    <t>Sítio Novo</t>
+  </si>
+  <si>
+    <t>Buritirana</t>
+  </si>
+  <si>
     <t>Balsas</t>
   </si>
   <si>
+    <t>Açailândia</t>
+  </si>
+  <si>
+    <t>Riachão</t>
+  </si>
+  <si>
+    <t>Bom Jesus Das Selvas</t>
+  </si>
+  <si>
+    <t>João Lisboa</t>
+  </si>
+  <si>
+    <t>Morros</t>
+  </si>
+  <si>
+    <t>Imperatriz</t>
+  </si>
+  <si>
+    <t>São João Dos Patos</t>
+  </si>
+  <si>
+    <t>Maracaçumé</t>
+  </si>
+  <si>
+    <t>Brejo</t>
+  </si>
+  <si>
+    <t>Santa Helena</t>
+  </si>
+  <si>
+    <t>Trizidela Do Vale</t>
+  </si>
+  <si>
+    <t>Timon</t>
+  </si>
+  <si>
+    <t>Barra Do Corda</t>
+  </si>
+  <si>
     <t>Esperantinópolis</t>
   </si>
   <si>
-    <t>B573</t>
-  </si>
-  <si>
-    <t>Turilândia</t>
-  </si>
-  <si>
-    <t>Açailândia</t>
+    <t>Santa Luzia do Paruá</t>
+  </si>
+  <si>
+    <t>São João Batista</t>
+  </si>
+  <si>
+    <t>Icatu</t>
+  </si>
+  <si>
+    <t>Campestre do Maranhão</t>
   </si>
   <si>
     <t>Alto Parnaíba</t>
   </si>
   <si>
-    <t>Timon</t>
+    <t>São João Do Paraíso</t>
+  </si>
+  <si>
+    <t>Bacuri</t>
+  </si>
+  <si>
+    <t>Pindaré-Mirim</t>
   </si>
 </sst>
 </file>
@@ -155,8 +269,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:N7" totalsRowShown="0">
-  <autoFilter ref="A1:N7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:N62" totalsRowShown="0">
+  <autoFilter ref="A1:N62"/>
   <tableColumns count="14">
     <tableColumn id="1" name="CID" dataDxfId="0"/>
     <tableColumn id="2" name="DT_DEATH" dataDxfId="1"/>
@@ -462,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -514,125 +628,131 @@
         <v>14</v>
       </c>
       <c r="B2" s="2">
-        <v>43055</v>
+        <v>44194</v>
       </c>
       <c r="C2" s="3">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D2" s="3">
         <v>21</v>
       </c>
       <c r="E2" s="3">
-        <v>210140</v>
+        <v>211190</v>
       </c>
       <c r="F2" s="3">
-        <v>61</v>
-      </c>
-      <c r="G2" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="H2" s="3">
         <v>1</v>
       </c>
       <c r="I2" s="3">
-        <v>94779</v>
+        <v>10634</v>
       </c>
       <c r="J2" s="3">
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="4">
-        <v>-8.236228444780563</v>
+        <v>-6.509751569290093</v>
       </c>
       <c r="M2" s="4">
-        <v>-46.34217144733357</v>
+        <v>-44.33893424731544</v>
       </c>
       <c r="N2" s="4">
-        <v>64.67187604637975</v>
+        <v>18.48813841552834</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2">
-        <v>42809</v>
+        <v>45301</v>
       </c>
       <c r="C3" s="3">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="D3" s="3">
         <v>21</v>
       </c>
       <c r="E3" s="3">
-        <v>210400</v>
+        <v>210860</v>
       </c>
       <c r="F3" s="3">
-        <v>84</v>
-      </c>
-      <c r="G3" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="H3" s="3">
         <v>1</v>
       </c>
       <c r="I3" s="3">
-        <v>16653</v>
+        <v>87919</v>
       </c>
       <c r="J3" s="3">
         <v>21</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L3" s="4">
-        <v>-4.89917549280705</v>
+        <v>-2.498106060393343</v>
       </c>
       <c r="M3" s="4">
-        <v>-44.89053284193997</v>
+        <v>-45.12691639291932</v>
       </c>
       <c r="N3" s="4">
-        <v>12.00013574797621</v>
+        <v>21.94334894165684</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>42999</v>
+        <v>43101</v>
       </c>
       <c r="C4" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D4" s="3">
         <v>21</v>
       </c>
       <c r="E4" s="3">
-        <v>211245</v>
+        <v>210330</v>
       </c>
       <c r="F4" s="3">
-        <v>50</v>
-      </c>
-      <c r="G4" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="H4" s="3">
         <v>1</v>
       </c>
       <c r="I4" s="3">
-        <v>25533</v>
+        <v>122597</v>
       </c>
       <c r="J4" s="3">
         <v>21</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L4" s="4">
-        <v>-2.159287133154328</v>
+        <v>-4.6069206197876</v>
       </c>
       <c r="M4" s="4">
-        <v>-45.43767435848336</v>
+        <v>-43.88570268446178</v>
       </c>
       <c r="N4" s="4">
-        <v>21.92669788891515</v>
+        <v>37.2517503844395</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -640,49 +760,51 @@
         <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>42946</v>
+        <v>44216</v>
       </c>
       <c r="C5" s="3">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="D5" s="3">
         <v>21</v>
       </c>
       <c r="E5" s="3">
-        <v>210005</v>
+        <v>211160</v>
       </c>
       <c r="F5" s="3">
-        <v>78</v>
-      </c>
-      <c r="G5" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="H5" s="3">
         <v>1</v>
       </c>
       <c r="I5" s="3">
-        <v>111339</v>
+        <v>19090</v>
       </c>
       <c r="J5" s="3">
         <v>21</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L5" s="4">
-        <v>-4.785949211555899</v>
+        <v>-7.01323858997755</v>
       </c>
       <c r="M5" s="4">
-        <v>-47.33224481604105</v>
+        <v>-45.69205091769385</v>
       </c>
       <c r="N5" s="4">
-        <v>43.00768845089489</v>
+        <v>34.57109239130914</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>42814</v>
+        <v>42999</v>
       </c>
       <c r="C6" s="3">
         <v>2017</v>
@@ -691,32 +813,32 @@
         <v>21</v>
       </c>
       <c r="E6" s="3">
-        <v>210050</v>
+        <v>211245</v>
       </c>
       <c r="F6" s="3">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="3">
         <v>1</v>
       </c>
       <c r="I6" s="3">
-        <v>11001</v>
+        <v>25533</v>
       </c>
       <c r="J6" s="3">
         <v>21</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L6" s="4">
-        <v>-9.508111429453159</v>
+        <v>-2.159287133154328</v>
       </c>
       <c r="M6" s="4">
-        <v>-46.21330020654692</v>
+        <v>-45.43767435848336</v>
       </c>
       <c r="N6" s="4">
-        <v>59.51845839193754</v>
+        <v>21.92669788891515</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -724,41 +846,2321 @@
         <v>14</v>
       </c>
       <c r="B7" s="2">
+        <v>43292</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D7" s="3">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3">
+        <v>210405</v>
+      </c>
+      <c r="F7" s="3">
+        <v>51</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>41355</v>
+      </c>
+      <c r="J7" s="3">
+        <v>21</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-6.782537809889291</v>
+      </c>
+      <c r="M7" s="4">
+        <v>-47.20131055905411</v>
+      </c>
+      <c r="N7" s="4">
+        <v>29.43148598855903</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2">
+        <v>43627</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D8" s="3">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3">
+        <v>210920</v>
+      </c>
+      <c r="F8" s="3">
+        <v>79</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>12734</v>
+      </c>
+      <c r="J8" s="3">
+        <v>21</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-3.08977913679622</v>
+      </c>
+      <c r="M8" s="4">
+        <v>-44.07781702935991</v>
+      </c>
+      <c r="N8" s="4">
+        <v>10.63616924156228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45494</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="3">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3">
+        <v>210535</v>
+      </c>
+      <c r="F9" s="3">
+        <v>71</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>14143</v>
+      </c>
+      <c r="J9" s="3">
+        <v>21</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-5.185046075391965</v>
+      </c>
+      <c r="M9" s="4">
+        <v>-45.67799245307465</v>
+      </c>
+      <c r="N9" s="4">
+        <v>19.89488984875839</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2">
+        <v>44806</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="3">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3">
+        <v>210760</v>
+      </c>
+      <c r="F10" s="3">
+        <v>87</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <v>44848</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D11" s="3">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3">
+        <v>210530</v>
+      </c>
+      <c r="F11" s="3">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>43172</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D12" s="3">
+        <v>21</v>
+      </c>
+      <c r="E12" s="3">
+        <v>210670</v>
+      </c>
+      <c r="F12" s="3">
+        <v>55</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>21000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>21</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-6.453786324692844</v>
+      </c>
+      <c r="M12" s="4">
+        <v>-44.95048457618886</v>
+      </c>
+      <c r="N12" s="4">
+        <v>52.06194181657886</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2">
+        <v>43250</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D13" s="3">
+        <v>21</v>
+      </c>
+      <c r="E13" s="3">
+        <v>210480</v>
+      </c>
+      <c r="F13" s="3">
+        <v>38</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>68876</v>
+      </c>
+      <c r="J13" s="3">
+        <v>21</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-5.840108418696903</v>
+      </c>
+      <c r="M13" s="4">
+        <v>-46.01474537001967</v>
+      </c>
+      <c r="N13" s="4">
+        <v>53.11352096013059</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2">
+        <v>44664</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="3">
+        <v>21</v>
+      </c>
+      <c r="E14" s="3">
+        <v>210197</v>
+      </c>
+      <c r="F14" s="3">
+        <v>47</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>44995</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2023</v>
+      </c>
+      <c r="D15" s="3">
+        <v>21</v>
+      </c>
+      <c r="E15" s="3">
+        <v>211120</v>
+      </c>
+      <c r="F15" s="3">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>43968</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D16" s="3">
+        <v>21</v>
+      </c>
+      <c r="E16" s="3">
+        <v>210480</v>
+      </c>
+      <c r="F16" s="3">
+        <v>84</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
+        <v>70065</v>
+      </c>
+      <c r="J16" s="3">
+        <v>21</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-5.840174675203325</v>
+      </c>
+      <c r="M16" s="4">
+        <v>-46.01485456306416</v>
+      </c>
+      <c r="N16" s="4">
+        <v>53.10468817492505</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45301</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D17" s="3">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3">
+        <v>210095</v>
+      </c>
+      <c r="F17" s="3">
+        <v>58</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>26191</v>
+      </c>
+      <c r="J17" s="3">
+        <v>21</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-5.027611038027202</v>
+      </c>
+      <c r="M17" s="4">
+        <v>-45.94590172219525</v>
+      </c>
+      <c r="N17" s="4">
+        <v>30.76547460830908</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2">
+        <v>44557</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D18" s="3">
+        <v>21</v>
+      </c>
+      <c r="E18" s="3">
+        <v>210240</v>
+      </c>
+      <c r="F18" s="3">
+        <v>30</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3">
+        <v>11255</v>
+      </c>
+      <c r="J18" s="3">
+        <v>21</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-2.876825571787843</v>
+      </c>
+      <c r="M18" s="4">
+        <v>-44.60363074181714</v>
+      </c>
+      <c r="N18" s="4">
+        <v>14.33023123340514</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="2">
+        <v>43681</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D19" s="3">
+        <v>21</v>
+      </c>
+      <c r="E19" s="3">
+        <v>211085</v>
+      </c>
+      <c r="F19" s="3">
+        <v>85</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3">
+        <v>11798</v>
+      </c>
+      <c r="J19" s="3">
+        <v>21</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-5.158462886605352</v>
+      </c>
+      <c r="M19" s="4">
+        <v>-47.3536695903786</v>
+      </c>
+      <c r="N19" s="4">
+        <v>15.41310480866893</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2">
+        <v>45430</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D20" s="3">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3">
+        <v>210480</v>
+      </c>
+      <c r="F20" s="3">
+        <v>75</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3">
+        <v>76578</v>
+      </c>
+      <c r="J20" s="3">
+        <v>21</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-5.840186992261929</v>
+      </c>
+      <c r="M20" s="4">
+        <v>-46.01485058938348</v>
+      </c>
+      <c r="N20" s="4">
+        <v>53.10446640179096</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="2">
+        <v>45384</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D21" s="3">
+        <v>21</v>
+      </c>
+      <c r="E21" s="3">
+        <v>210480</v>
+      </c>
+      <c r="F21" s="3">
+        <v>76</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>76578</v>
+      </c>
+      <c r="J21" s="3">
+        <v>21</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-5.840186992261929</v>
+      </c>
+      <c r="M21" s="4">
+        <v>-46.01485058938348</v>
+      </c>
+      <c r="N21" s="4">
+        <v>53.10446640179096</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="2">
+        <v>44072</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D22" s="3">
+        <v>21</v>
+      </c>
+      <c r="E22" s="3">
+        <v>210870</v>
+      </c>
+      <c r="F22" s="3">
+        <v>77</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>21379</v>
+      </c>
+      <c r="J22" s="3">
+        <v>21</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-3.851517121330533</v>
+      </c>
+      <c r="M22" s="4">
+        <v>-45.09313209369893</v>
+      </c>
+      <c r="N22" s="4">
+        <v>13.16737902822803</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2">
+        <v>45508</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D23" s="3">
+        <v>21</v>
+      </c>
+      <c r="E23" s="3">
+        <v>211180</v>
+      </c>
+      <c r="F23" s="3">
+        <v>101</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>17457</v>
+      </c>
+      <c r="J23" s="3">
+        <v>21</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-6.227627501989852</v>
+      </c>
+      <c r="M23" s="4">
+        <v>-46.59575201425359</v>
+      </c>
+      <c r="N23" s="4">
+        <v>31.4895155226271</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2">
+        <v>43468</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D24" s="3">
+        <v>21</v>
+      </c>
+      <c r="E24" s="3">
+        <v>210235</v>
+      </c>
+      <c r="F24" s="3">
+        <v>68</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <v>15430</v>
+      </c>
+      <c r="J24" s="3">
+        <v>21</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-5.51798430669192</v>
+      </c>
+      <c r="M24" s="4">
+        <v>-47.06134717008451</v>
+      </c>
+      <c r="N24" s="4">
+        <v>16.14564587992207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="2">
+        <v>43771</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D25" s="3">
+        <v>21</v>
+      </c>
+      <c r="E25" s="3">
+        <v>210407</v>
+      </c>
+      <c r="F25" s="3">
+        <v>70</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="2">
+        <v>44091</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D26" s="3">
+        <v>21</v>
+      </c>
+      <c r="E26" s="3">
+        <v>210140</v>
+      </c>
+      <c r="F26" s="3">
+        <v>81</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
+        <v>95929</v>
+      </c>
+      <c r="J26" s="3">
+        <v>21</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-8.236293169911136</v>
+      </c>
+      <c r="M26" s="4">
+        <v>-46.34220993445859</v>
+      </c>
+      <c r="N26" s="4">
+        <v>64.66928536210257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="2">
+        <v>42946</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2017</v>
+      </c>
+      <c r="D27" s="3">
+        <v>21</v>
+      </c>
+      <c r="E27" s="3">
+        <v>210005</v>
+      </c>
+      <c r="F27" s="3">
+        <v>78</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
+        <v>111339</v>
+      </c>
+      <c r="J27" s="3">
+        <v>21</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-4.785949211555899</v>
+      </c>
+      <c r="M27" s="4">
+        <v>-47.33224481604105</v>
+      </c>
+      <c r="N27" s="4">
+        <v>43.00768845089489</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45589</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D28" s="3">
+        <v>21</v>
+      </c>
+      <c r="E28" s="3">
+        <v>210670</v>
+      </c>
+      <c r="F28" s="3">
+        <v>66</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <v>21518</v>
+      </c>
+      <c r="J28" s="3">
+        <v>21</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="4">
+        <v>-6.453702504021277</v>
+      </c>
+      <c r="M28" s="4">
+        <v>-44.95044967406259</v>
+      </c>
+      <c r="N28" s="4">
+        <v>52.06680780414857</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="2">
+        <v>43239</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D29" s="3">
+        <v>21</v>
+      </c>
+      <c r="E29" s="3">
+        <v>210950</v>
+      </c>
+      <c r="F29" s="3">
+        <v>73</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
+        <v>20243</v>
+      </c>
+      <c r="J29" s="3">
+        <v>21</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L29" s="4">
+        <v>-7.597686447837996</v>
+      </c>
+      <c r="M29" s="4">
+        <v>-46.65241436765139</v>
+      </c>
+      <c r="N29" s="4">
+        <v>45.03790226071004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45072</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2023</v>
+      </c>
+      <c r="D30" s="3">
+        <v>21</v>
+      </c>
+      <c r="E30" s="3">
+        <v>210060</v>
+      </c>
+      <c r="F30" s="3">
+        <v>74</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="2">
+        <v>43625</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D31" s="3">
+        <v>21</v>
+      </c>
+      <c r="E31" s="3">
+        <v>210203</v>
+      </c>
+      <c r="F31" s="3">
+        <v>38</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
+        <v>34028</v>
+      </c>
+      <c r="J31" s="3">
+        <v>21</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L31" s="4">
+        <v>-4.60074294764658</v>
+      </c>
+      <c r="M31" s="4">
+        <v>-46.68861288112049</v>
+      </c>
+      <c r="N31" s="4">
+        <v>29.19238351392249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="2">
+        <v>43719</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D32" s="3">
+        <v>21</v>
+      </c>
+      <c r="E32" s="3">
+        <v>210550</v>
+      </c>
+      <c r="F32" s="3">
+        <v>82</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3">
+        <v>23632</v>
+      </c>
+      <c r="J32" s="3">
+        <v>21</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L32" s="4">
+        <v>-5.229361864523688</v>
+      </c>
+      <c r="M32" s="4">
+        <v>-47.12643086640992</v>
+      </c>
+      <c r="N32" s="4">
+        <v>19.01919372713862</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2">
+        <v>45650</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D33" s="3">
+        <v>21</v>
+      </c>
+      <c r="E33" s="3">
+        <v>210710</v>
+      </c>
+      <c r="F33" s="3">
+        <v>47</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
+        <v>18994</v>
+      </c>
+      <c r="J33" s="3">
+        <v>21</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="4">
+        <v>-2.973945449849574</v>
+      </c>
+      <c r="M33" s="4">
+        <v>-43.776881046696</v>
+      </c>
+      <c r="N33" s="4">
+        <v>23.35015550075169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="2">
+        <v>45352</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D34" s="3">
+        <v>21</v>
+      </c>
+      <c r="E34" s="3">
+        <v>210530</v>
+      </c>
+      <c r="F34" s="3">
+        <v>46</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3">
+        <v>285146</v>
+      </c>
+      <c r="J34" s="3">
+        <v>21</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="4">
+        <v>-5.339716038695142</v>
+      </c>
+      <c r="M34" s="4">
+        <v>-47.57519570356587</v>
+      </c>
+      <c r="N34" s="4">
+        <v>20.8883487643149</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="2">
+        <v>43306</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D35" s="3">
+        <v>21</v>
+      </c>
+      <c r="E35" s="3">
+        <v>211110</v>
+      </c>
+      <c r="F35" s="3">
+        <v>72</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
+        <v>25860</v>
+      </c>
+      <c r="J35" s="3">
+        <v>21</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L35" s="4">
+        <v>-6.55965219511627</v>
+      </c>
+      <c r="M35" s="4">
+        <v>-43.63814178357608</v>
+      </c>
+      <c r="N35" s="4">
+        <v>21.72320026517214</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="2">
+        <v>43814</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D36" s="3">
+        <v>21</v>
+      </c>
+      <c r="E36" s="3">
+        <v>210632</v>
+      </c>
+      <c r="F36" s="3">
+        <v>69</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="3">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
+        <v>21395</v>
+      </c>
+      <c r="J36" s="3">
+        <v>21</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L36" s="4">
+        <v>-1.984190899179971</v>
+      </c>
+      <c r="M36" s="4">
+        <v>-45.99391008173745</v>
+      </c>
+      <c r="N36" s="4">
+        <v>14.22062631617895</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="2">
+        <v>43775</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D37" s="3">
+        <v>21</v>
+      </c>
+      <c r="E37" s="3">
+        <v>210210</v>
+      </c>
+      <c r="F37" s="3">
+        <v>88</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="3">
+        <v>1</v>
+      </c>
+      <c r="I37" s="3">
+        <v>36397</v>
+      </c>
+      <c r="J37" s="3">
+        <v>21</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L37" s="4">
+        <v>-3.687144914019086</v>
+      </c>
+      <c r="M37" s="4">
+        <v>-42.82834769170847</v>
+      </c>
+      <c r="N37" s="4">
+        <v>18.49774322566661</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="2">
+        <v>43987</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D38" s="3">
+        <v>21</v>
+      </c>
+      <c r="E38" s="3">
+        <v>210980</v>
+      </c>
+      <c r="F38" s="3">
+        <v>86</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="3">
+        <v>42483</v>
+      </c>
+      <c r="J38" s="3">
+        <v>21</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L38" s="4">
+        <v>-2.418936674525883</v>
+      </c>
+      <c r="M38" s="4">
+        <v>-45.37121256316365</v>
+      </c>
+      <c r="N38" s="4">
+        <v>26.39503185984245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="2">
+        <v>43384</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D39" s="3">
+        <v>21</v>
+      </c>
+      <c r="E39" s="3">
+        <v>211223</v>
+      </c>
+      <c r="F39" s="3">
+        <v>27</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="3">
+        <v>1</v>
+      </c>
+      <c r="I39" s="3">
+        <v>21885</v>
+      </c>
+      <c r="J39" s="3">
+        <v>21</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" s="4">
+        <v>-4.539246577943071</v>
+      </c>
+      <c r="M39" s="4">
+        <v>-44.68164375876234</v>
+      </c>
+      <c r="N39" s="4">
+        <v>9.638890539803851</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="2">
+        <v>44410</v>
+      </c>
+      <c r="C40" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D40" s="3">
+        <v>21</v>
+      </c>
+      <c r="E40" s="3">
+        <v>210530</v>
+      </c>
+      <c r="F40" s="3">
+        <v>72</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="3">
+        <v>1</v>
+      </c>
+      <c r="I40" s="3">
+        <v>259980</v>
+      </c>
+      <c r="J40" s="3">
+        <v>21</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L40" s="4">
+        <v>-5.341843607849938</v>
+      </c>
+      <c r="M40" s="4">
+        <v>-47.5739220201685</v>
+      </c>
+      <c r="N40" s="4">
+        <v>22.10179352014185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="2">
+        <v>44575</v>
+      </c>
+      <c r="C41" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D41" s="3">
+        <v>21</v>
+      </c>
+      <c r="E41" s="3">
+        <v>211070</v>
+      </c>
+      <c r="F41" s="3">
+        <v>93</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="2">
+        <v>44910</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D42" s="3">
+        <v>21</v>
+      </c>
+      <c r="E42" s="3">
+        <v>211130</v>
+      </c>
+      <c r="F42" s="3">
+        <v>56</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="2">
+        <v>44449</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D43" s="3">
+        <v>21</v>
+      </c>
+      <c r="E43" s="3">
+        <v>210235</v>
+      </c>
+      <c r="F43" s="3">
+        <v>67</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1</v>
+      </c>
+      <c r="I43" s="3">
+        <v>15503</v>
+      </c>
+      <c r="J43" s="3">
+        <v>21</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L43" s="4">
+        <v>-5.517936539423499</v>
+      </c>
+      <c r="M43" s="4">
+        <v>-47.06225982786495</v>
+      </c>
+      <c r="N43" s="4">
+        <v>16.6514249120096</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="2">
         <v>42810</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C44" s="3">
         <v>2017</v>
       </c>
-      <c r="D7" s="3">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="D44" s="3">
+        <v>21</v>
+      </c>
+      <c r="E44" s="3">
         <v>211220</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F44" s="3">
         <v>63</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3">
+      <c r="G44" s="1"/>
+      <c r="H44" s="3">
+        <v>1</v>
+      </c>
+      <c r="I44" s="3">
         <v>167619</v>
       </c>
-      <c r="J7" s="3">
-        <v>21</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="4">
+      <c r="J44" s="3">
+        <v>21</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="4">
         <v>-5.185249178435842</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M44" s="4">
         <v>-42.98083617644607</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N44" s="4">
         <v>23.70015696660288</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="2">
+        <v>43243</v>
+      </c>
+      <c r="C45" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D45" s="3">
+        <v>21</v>
+      </c>
+      <c r="E45" s="3">
+        <v>210160</v>
+      </c>
+      <c r="F45" s="3">
+        <v>67</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" s="3">
+        <v>87794</v>
+      </c>
+      <c r="J45" s="3">
+        <v>21</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L45" s="4">
+        <v>-5.504104173372463</v>
+      </c>
+      <c r="M45" s="4">
+        <v>-45.18321561345769</v>
+      </c>
+      <c r="N45" s="4">
+        <v>40.62356408320872</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="2">
+        <v>45515</v>
+      </c>
+      <c r="C46" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D46" s="3">
+        <v>21</v>
+      </c>
+      <c r="E46" s="3">
+        <v>210005</v>
+      </c>
+      <c r="F46" s="3">
+        <v>72</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1</v>
+      </c>
+      <c r="I46" s="3">
+        <v>110506</v>
+      </c>
+      <c r="J46" s="3">
+        <v>21</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="4">
+        <v>-4.785827728022469</v>
+      </c>
+      <c r="M46" s="4">
+        <v>-47.33221469457047</v>
+      </c>
+      <c r="N46" s="4">
+        <v>43.00259975493859</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="2">
+        <v>44534</v>
+      </c>
+      <c r="C47" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D47" s="3">
+        <v>21</v>
+      </c>
+      <c r="E47" s="3">
+        <v>210530</v>
+      </c>
+      <c r="F47" s="3">
+        <v>84</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" s="3">
+        <v>259980</v>
+      </c>
+      <c r="J47" s="3">
+        <v>21</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L47" s="4">
+        <v>-5.341843607849938</v>
+      </c>
+      <c r="M47" s="4">
+        <v>-47.5739220201685</v>
+      </c>
+      <c r="N47" s="4">
+        <v>22.10179352014185</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="2">
+        <v>42809</v>
+      </c>
+      <c r="C48" s="3">
+        <v>2017</v>
+      </c>
+      <c r="D48" s="3">
+        <v>21</v>
+      </c>
+      <c r="E48" s="3">
+        <v>210400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>84</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="I48" s="3">
+        <v>16653</v>
+      </c>
+      <c r="J48" s="3">
+        <v>21</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L48" s="4">
+        <v>-4.89917549280705</v>
+      </c>
+      <c r="M48" s="4">
+        <v>-44.89053284193997</v>
+      </c>
+      <c r="N48" s="4">
+        <v>12.00013574797621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="2">
+        <v>44500</v>
+      </c>
+      <c r="C49" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D49" s="3">
+        <v>21</v>
+      </c>
+      <c r="E49" s="3">
+        <v>211003</v>
+      </c>
+      <c r="F49" s="3">
+        <v>68</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" s="3">
+        <v>25487</v>
+      </c>
+      <c r="J49" s="3">
+        <v>21</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L49" s="4">
+        <v>-2.540097306289178</v>
+      </c>
+      <c r="M49" s="4">
+        <v>-45.77285512630142</v>
+      </c>
+      <c r="N49" s="4">
+        <v>18.39430283944316</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="2">
+        <v>44306</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D50" s="3">
+        <v>21</v>
+      </c>
+      <c r="E50" s="3">
+        <v>211100</v>
+      </c>
+      <c r="F50" s="3">
+        <v>43</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" s="3">
+        <v>20736</v>
+      </c>
+      <c r="J50" s="3">
+        <v>21</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="4">
+        <v>-3.005690414188858</v>
+      </c>
+      <c r="M50" s="4">
+        <v>-44.76592315791535</v>
+      </c>
+      <c r="N50" s="4">
+        <v>14.94309247868446</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="2">
+        <v>44227</v>
+      </c>
+      <c r="C51" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D51" s="3">
+        <v>21</v>
+      </c>
+      <c r="E51" s="3">
+        <v>210510</v>
+      </c>
+      <c r="F51" s="3">
+        <v>87</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="I51" s="3">
+        <v>27423</v>
+      </c>
+      <c r="J51" s="3">
+        <v>21</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L51" s="4">
+        <v>-2.643751866103748</v>
+      </c>
+      <c r="M51" s="4">
+        <v>-43.86115062664651</v>
+      </c>
+      <c r="N51" s="4">
+        <v>19.94525764532731</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45352</v>
+      </c>
+      <c r="C52" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D52" s="3">
+        <v>21</v>
+      </c>
+      <c r="E52" s="3">
+        <v>210255</v>
+      </c>
+      <c r="F52" s="3">
+        <v>61</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1</v>
+      </c>
+      <c r="I52" s="3">
+        <v>12553</v>
+      </c>
+      <c r="J52" s="3">
+        <v>21</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L52" s="4">
+        <v>-6.176231499946478</v>
+      </c>
+      <c r="M52" s="4">
+        <v>-47.26382200809544</v>
+      </c>
+      <c r="N52" s="4">
+        <v>13.97925299016578</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="2">
+        <v>44718</v>
+      </c>
+      <c r="C53" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D53" s="3">
+        <v>21</v>
+      </c>
+      <c r="E53" s="3">
+        <v>211153</v>
+      </c>
+      <c r="F53" s="3">
+        <v>86</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45165</v>
+      </c>
+      <c r="C54" s="3">
+        <v>2023</v>
+      </c>
+      <c r="D54" s="3">
+        <v>21</v>
+      </c>
+      <c r="E54" s="3">
+        <v>210203</v>
+      </c>
+      <c r="F54" s="3">
+        <v>56</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="2">
+        <v>43055</v>
+      </c>
+      <c r="C55" s="3">
+        <v>2017</v>
+      </c>
+      <c r="D55" s="3">
+        <v>21</v>
+      </c>
+      <c r="E55" s="3">
+        <v>210140</v>
+      </c>
+      <c r="F55" s="3">
+        <v>61</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
+        <v>94779</v>
+      </c>
+      <c r="J55" s="3">
+        <v>21</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L55" s="4">
+        <v>-8.236228444780563</v>
+      </c>
+      <c r="M55" s="4">
+        <v>-46.34217144733357</v>
+      </c>
+      <c r="N55" s="4">
+        <v>64.67187604637975</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="2">
+        <v>42814</v>
+      </c>
+      <c r="C56" s="3">
+        <v>2017</v>
+      </c>
+      <c r="D56" s="3">
+        <v>21</v>
+      </c>
+      <c r="E56" s="3">
+        <v>210050</v>
+      </c>
+      <c r="F56" s="3">
+        <v>71</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3">
+        <v>11001</v>
+      </c>
+      <c r="J56" s="3">
+        <v>21</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56" s="4">
+        <v>-9.508111429453159</v>
+      </c>
+      <c r="M56" s="4">
+        <v>-46.21330020654692</v>
+      </c>
+      <c r="N56" s="4">
+        <v>59.51845839193754</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45220</v>
+      </c>
+      <c r="C57" s="3">
+        <v>2023</v>
+      </c>
+      <c r="D57" s="3">
+        <v>21</v>
+      </c>
+      <c r="E57" s="3">
+        <v>210675</v>
+      </c>
+      <c r="F57" s="3">
+        <v>66</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="2">
+        <v>43613</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D58" s="3">
+        <v>21</v>
+      </c>
+      <c r="E58" s="3">
+        <v>211105</v>
+      </c>
+      <c r="F58" s="3">
+        <v>73</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="I58" s="3">
+        <v>11177</v>
+      </c>
+      <c r="J58" s="3">
+        <v>21</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="4">
+        <v>-6.463688861473194</v>
+      </c>
+      <c r="M58" s="4">
+        <v>-46.90065887481664</v>
+      </c>
+      <c r="N58" s="4">
+        <v>25.57577725242119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="2">
+        <v>43240</v>
+      </c>
+      <c r="C59" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D59" s="3">
+        <v>21</v>
+      </c>
+      <c r="E59" s="3">
+        <v>210050</v>
+      </c>
+      <c r="F59" s="3">
+        <v>67</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" s="3">
+        <v>11168</v>
+      </c>
+      <c r="J59" s="3">
+        <v>21</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L59" s="4">
+        <v>-9.508118088350313</v>
+      </c>
+      <c r="M59" s="4">
+        <v>-46.21329608964567</v>
+      </c>
+      <c r="N59" s="4">
+        <v>59.51805652608211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="2">
+        <v>43101</v>
+      </c>
+      <c r="C60" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D60" s="3">
+        <v>21</v>
+      </c>
+      <c r="E60" s="3">
+        <v>210130</v>
+      </c>
+      <c r="F60" s="3">
+        <v>59</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1</v>
+      </c>
+      <c r="I60" s="3">
+        <v>18508</v>
+      </c>
+      <c r="J60" s="3">
+        <v>21</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L60" s="4">
+        <v>-1.683167198458953</v>
+      </c>
+      <c r="M60" s="4">
+        <v>-45.16901184833636</v>
+      </c>
+      <c r="N60" s="4">
+        <v>16.74237075436688</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="2">
+        <v>43719</v>
+      </c>
+      <c r="C61" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D61" s="3">
+        <v>21</v>
+      </c>
+      <c r="E61" s="3">
+        <v>210530</v>
+      </c>
+      <c r="F61" s="3">
+        <v>78</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="I61" s="3">
+        <v>258682</v>
+      </c>
+      <c r="J61" s="3">
+        <v>21</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L61" s="4">
+        <v>-5.339736359494743</v>
+      </c>
+      <c r="M61" s="4">
+        <v>-47.57521618495749</v>
+      </c>
+      <c r="N61" s="4">
+        <v>20.89093347527377</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="2">
+        <v>44269</v>
+      </c>
+      <c r="C62" s="3">
+        <v>2021</v>
+      </c>
+      <c r="D62" s="3">
+        <v>21</v>
+      </c>
+      <c r="E62" s="3">
+        <v>210850</v>
+      </c>
+      <c r="F62" s="3">
+        <v>81</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" s="3">
+        <v>33186</v>
+      </c>
+      <c r="J62" s="3">
+        <v>21</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L62" s="4">
+        <v>-3.689292805862562</v>
+      </c>
+      <c r="M62" s="4">
+        <v>-45.43571644344005</v>
+      </c>
+      <c r="N62" s="4">
+        <v>10.01140499371733</v>
       </c>
     </row>
   </sheetData>
